--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U6</t>
+          <t>AU3005</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,83 +482,83 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Osannolikt kort (22 tecken): '- Bildproduktion 60 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Audiovisuella studier: Kunskapsproduktion och gestaltning'</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AU3005</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>GBQ29E</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Osannolikt kort (22 tecken): '- Historia III 22,5 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Bildproduktion: Teori och Metod'</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AHI29R</t>
+          <t>GBQ2AZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Osannolikt kort (22 tecken): '- Historia III 22,5 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Det cinematiska språket: Mise-en-scène'</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AZ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GHI33T</t>
+          <t>GBQ2U6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Osannolikt kort (20 tecken): '- Historia I 22,5 hp'</t>
+          <t>Osannolikt kort (22 tecken): '- Bildproduktion 60 hp'</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GHI3CP</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Osannolikt kort (22 tecken): '- Historia III 22,5 hp'</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>AHI29R</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Osannolikt kort (24 tecken): '- 60 hp i kulturgeografi'</t>
+          <t>Osannolikt kort (22 tecken): '- Historia III 22,5 hp'</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KG2005</t>
+          <t>GHI33T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -649,78 +649,78 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Osannolikt kort (24 tecken): '- 60 hp i kulturgeografi'</t>
+          <t>Osannolikt kort (20 tecken): '- Historia I 22,5 hp'</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>GHI3CP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stor sv/en-längdskillnad</t>
+          <t>Osannolikt kort innehåll</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Längdskillnad sv 32 tecken vs en 79 tecken (×2.5)</t>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PE1052</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Osannolikt kort (19 tecken): '- Ingen behörighet.'</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Demography and Markets for Tourism'</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -730,51 +730,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Osannolikt kort (24 tecken): '- 60 hp i kulturgeografi'</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>KG2005</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Stor sv/en-längdskillnad</t>
+          <t>Osannolikt kort innehåll</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Längdskillnad sv 65 tecken vs en 132 tecken (×2.0)</t>
+          <t>Osannolikt kort (24 tecken): '- 60 hp i kulturgeografi'</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>APG2BK</t>
+          <t>KG3010</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -784,78 +784,78 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Längdskillnad sv 47 tecken vs en 99 tecken (×2.1)</t>
+          <t>Längdskillnad sv 32 tecken vs en 79 tecken (×2.5)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GPG22J</t>
+          <t>GLP29S</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Radioproduktion'</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GPG27X</t>
+          <t>GLP2KH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar okänd HDa-kurs</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Refererad kurs hittas ej i vaulten: 'Radioproduktion'</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GPG3CN</t>
+          <t>PE1052</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Osannolikt kort (19 tecken): '- Ingen behörighet.'</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1052</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Stor sv/en-längdskillnad</t>
+          <t>Osannolikt kort innehåll</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Längdskillnad sv 48 tecken vs en 122 tecken (×2.5)</t>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,78 +919,78 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Längdskillnad sv 240 tecken vs en 31 tecken (×7.7)</t>
+          <t>Längdskillnad sv 65 tecken vs en 132 tecken (×2.0)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GRK3CQ</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Längdskillnad sv 47 tecken vs en 99 tecken (×2.1)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>GPG22J</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stor sv/en-längdskillnad</t>
+          <t>Osannolikt kort innehåll</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Längdskillnad sv 108 tecken vs en 54 tecken (×2.0)</t>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>GPG27X</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Osannolikt kort (14 tecken): '- Socialrätt I'</t>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>GPG3CN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,78 +1027,78 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Osannolikt kort (22 tecken): '- Sociologi I, 22,5 hp'</t>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Osannolikt kort (23 tecken): '- 30 hp Turismvetenskap'</t>
+          <t>Längdskillnad sv 48 tecken vs en 122 tecken (×2.5)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Osannolikt kort (7 tecken): '- 60 hp'</t>
+          <t>Längdskillnad sv 240 tecken vs en 31 tecken (×7.7)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GTR2DP</t>
+          <t>GRK3CQ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,51 +1108,51 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Osannolikt kort (7 tecken): '- 60 hp'</t>
+          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GTR2G6</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Osannolikt kort (7 tecken): '- 60 hp'</t>
+          <t>Längdskillnad sv 108 tecken vs en 54 tecken (×2.0)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1162,44 +1162,233 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Osannolikt kort (23 tecken): '- 30 hp Turismvetenskap'</t>
+          <t>Osannolikt kort (14 tecken): '- Socialrätt I'</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>RV1055</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Refererar okänd HDa-kurs</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten: 'Perspektiv på företagande'</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GSO2XU</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Osannolikt kort (22 tecken): '- Sociologi I, 22,5 hp'</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Osannolikt kort (23 tecken): '- 30 hp Turismvetenskap'</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DG</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Osannolikt kort (7 tecken): '- 60 hp'</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DP</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Osannolikt kort (7 tecken): '- 60 hp'</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GTR2G6</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Osannolikt kort (7 tecken): '- 60 hp'</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>GTR2UM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Osannolikt kort (23 tecken): '- 30 hp Turismvetenskap'</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>TR1035</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>TRU</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Osannolikt kort innehåll</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Osannolikt kort (23 tecken): '- 30 hp Turismvetenskap'</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E28"/>
+  <autoFilter ref="A1:E35"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1255,6 +1444,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -482,12 +482,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Refererar okänd HDa-kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Audiovisuella studier: Kunskapsproduktion och gestaltning'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Audiovisuella studier: Kunskapsproduktion och gestaltning'</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Refererar okänd HDa-kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Bildproduktion: Teori och Metod'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Bildproduktion: Teori och Metod'</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Refererar okänd HDa-kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Det cinematiska språket: Mise-en-scène'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Det cinematiska språket: Mise-en-scène'</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -553,228 +553,228 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U6</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Osannolikt kort (22 tecken): '- Bildproduktion 60 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Demography and Markets for Tourism'</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>KG3010</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Osannolikt kort (22 tecken): '- Historia III 22,5 hp'</t>
+          <t>Längdskillnad sv 32 tecken vs en 79 tecken (×2.5)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AHI29R</t>
+          <t>GLP29S</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Osannolikt kort (22 tecken): '- Historia III 22,5 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Radioproduktion'</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GHI33T</t>
+          <t>GLP2KH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Osannolikt kort (20 tecken): '- Historia I 22,5 hp'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Radioproduktion'</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GHI3CP</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
+          <t>Längdskillnad sv 65 tecken vs en 132 tecken (×2.0)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Refererar okänd HDa-kurs</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Demography and Markets for Tourism'</t>
+          <t>Längdskillnad sv 47 tecken vs en 99 tecken (×2.1)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Osannolikt kort (24 tecken): '- 60 hp i kulturgeografi'</t>
+          <t>Längdskillnad sv 48 tecken vs en 122 tecken (×2.5)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KG2005</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Osannolikt kort innehåll</t>
+          <t>Stor sv/en-längdskillnad</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Osannolikt kort (24 tecken): '- 60 hp i kulturgeografi'</t>
+          <t>Längdskillnad sv 240 tecken vs en 31 tecken (×7.7)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -784,611 +784,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Längdskillnad sv 32 tecken vs en 79 tecken (×2.5)</t>
+          <t>Längdskillnad sv 108 tecken vs en 54 tecken (×2.0)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GLP29S</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Refererar okänd HDa-kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Radioproduktion'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Perspektiv på företagande'</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>GLP2KH</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LPU</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Refererar okänd HDa-kurs</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Radioproduktion'</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>PE1052</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PEA</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (19 tecken): '- Ingen behörighet.'</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1052</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>APG2AA</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>APG2AJ</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 65 tecken vs en 132 tecken (×2.0)</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>APG2BK</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 47 tecken vs en 99 tecken (×2.1)</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>GPG22J</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>GPG27X</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>GPG3CN</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>GPG3FT</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 48 tecken vs en 122 tecken (×2.5)</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>PG2043</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 240 tecken vs en 31 tecken (×7.7)</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>GRK3CQ</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>RKA</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (13 tecken): '- Lärarexamen'</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>RK3043</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>RKA</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 108 tecken vs en 54 tecken (×2.0)</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>RV1047</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (14 tecken): '- Socialrätt I'</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>RV1055</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Refererar okänd HDa-kurs</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten: 'Perspektiv på företagande'</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>GSO2XU</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SOA</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (22 tecken): '- Sociologi I, 22,5 hp'</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>GTR29Q</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (23 tecken): '- 30 hp Turismvetenskap'</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>GTR2DG</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (7 tecken): '- 60 hp'</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>GTR2DP</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (7 tecken): '- 60 hp'</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>GTR2G6</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (7 tecken): '- 60 hp'</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>GTR2UM</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (23 tecken): '- 30 hp Turismvetenskap'</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TR1035</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Osannolikt kort innehåll</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Osannolikt kort (23 tecken): '- 30 hp Turismvetenskap'</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E35"/>
+  <autoFilter ref="A1:E14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1416,48 +849,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,34 +580,34 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>GLP29S</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stor sv/en-längdskillnad</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Längdskillnad sv 32 tecken vs en 79 tecken (×2.5)</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Radioproduktion'</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GLP29S</t>
+          <t>GLP2KH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -627,19 +627,19 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GLP2KH</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -649,179 +649,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Radioproduktion'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Perspektiv på företagande'</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>APG2AJ</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 65 tecken vs en 132 tecken (×2.0)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>APG2BK</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 47 tecken vs en 99 tecken (×2.1)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>GPG3FT</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 48 tecken vs en 122 tecken (×2.5)</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>PG2043</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 240 tecken vs en 31 tecken (×7.7)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>RK3043</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>RKA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Stor sv/en-längdskillnad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Längdskillnad sv 108 tecken vs en 54 tecken (×2.0)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>RV1055</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Refererar troligen nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Perspektiv på företagande'</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E14"/>
+  <autoFilter ref="A1:E8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -837,18 +675,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,61 +472,61 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AU3005</t>
+          <t>ABP253</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Audiovisuella studier: Kunskapsproduktion och gestaltning'</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AU3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP253</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GBQ29E</t>
+          <t>ABP254</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Bildproduktion: Teori och Metod'</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP254</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GBQ2AZ</t>
+          <t>AU3005</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Det cinematiska språket: Mise-en-scène'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Audiovisuella studier: Kunskapsproduktion och gestaltning'</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AU3005</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>GBQ29E</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Demography and Markets for Tourism'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Bildproduktion: Teori och Metod'</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GLP29S</t>
+          <t>GBQ2AZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -595,71 +595,1043 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Radioproduktion'</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Det cinematiska språket: Mise-en-scène'</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AZ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GLP2KH</t>
+          <t>GBQ2NP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Radioproduktion'</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>GBQ2QB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2U9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2UD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>AHI23V</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AHI23W</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>HI2014</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>KG1016</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Demography and Markets for Tourism'</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>KG1016</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>`Tourism and Destination Development – An Introduction` → `TR1009` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>KG1022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`Nordisk turism` → `KG1026` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>KG1027</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>`Introduktion till Javaprogrammering` → `IK1046` (nedlagd 2020-06-11); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GLP29S</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Radioproduktion'</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GLP29S</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GLP2KH</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Refererar troligen nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Radioproduktion'</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GLP2KH</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>LP1054</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>`Audiovisuell representation I` → `LP1017` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>LP1054</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>`Audiovisuell representation II` → `LP1020` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>GMN3EJ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MPR</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>`Audioteknologi` → `LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>GMN3F2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MPR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>GPA354</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>`Arbetsrättens grunder` → `PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>APG246</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>APG247</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>APG275</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`Matematik 2a för grundlärare F-3` → `MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>APG275</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>`Matematik 2b för grundlärare F-3` → `MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>APG276</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>`Matematik 2a för grundlärare 4-6` → `MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>APG276</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>`Matematik 2b för grundlärare 4-6` → `MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>PG3025</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ARK25B</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ARK25C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ARK29H</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ARK29J</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>GRK2R7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>GRK2R8</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RK3043</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>GRV266</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>`Extern redovisning` → `FEA037` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>RV1003</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>`Extern redovisning` → `FEA037` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>RV1055</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>RVA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Perspektiv på företagande'</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RV1055</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>`Perspektiv på företagande` → `FEA058` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E44"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -675,6 +1647,78 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GBQ29E</t>
+          <t>GBQ2NP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,24 +563,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Bildproduktion: Teori och Metod'</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GBQ2AZ</t>
+          <t>GBQ2QB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -590,24 +590,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Det cinematiska språket: Mise-en-scène'</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2QB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GBQ2NP</t>
+          <t>GBQ2U9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -627,14 +627,14 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GBQ2QB</t>
+          <t>GBQ2UD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -654,19 +654,19 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2QB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U9</t>
+          <t>AHI23V</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -681,19 +681,19 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GBQ2UD</t>
+          <t>AHI23W</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AHI23V</t>
+          <t>HI2014</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -735,46 +735,46 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AHI23W</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Demography and Markets for Tourism'</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HI2014</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Tourism and Destination Development – An Introduction` → `TR1009` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>KG1022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -806,24 +806,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Demography and Markets for Tourism'</t>
+          <t>`Nordisk turism` → `KG1026` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>KG1027</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Tourism and Destination Development – An Introduction` → `TR1009` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
+          <t>`Introduktion till Javaprogrammering` → `IK1046` (nedlagd 2020-06-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KG1022</t>
+          <t>GLP29S</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Nordisk turism` → `KG1026` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
+          <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KG1027</t>
+          <t>GLP2KH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Introduktion till Javaprogrammering` → `IK1046` (nedlagd 2020-06-11); förkunskap nämner nedlagd kurs</t>
+          <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GLP29S</t>
+          <t>LP1054</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -914,24 +914,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Radioproduktion'</t>
+          <t>`Audiovisuell representation I` → `LP1017` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GLP29S</t>
+          <t>LP1054</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,51 +946,51 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
+          <t>`Audiovisuell representation II` → `LP1020` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GLP2KH</t>
+          <t>GMN3EJ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Radioproduktion'</t>
+          <t>`Audioteknologi` → `LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GLP2KH</t>
+          <t>GMN3F2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>LP1054</t>
+          <t>GPA354</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`Audiovisuell representation I` → `LP1017` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Arbetsrättens grunder` → `PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>LP1054</t>
+          <t>APG246</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`Audiovisuell representation II` → `LP1020` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GMN3EJ</t>
+          <t>APG247</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`Audioteknologi` → `LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GMN3F2</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Matematik 2a för grundlärare F-3` → `MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GPA354</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`Arbetsrättens grunder` → `PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`Matematik 2b för grundlärare F-3` → `MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>APG246</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Matematik 2a för grundlärare 4-6` → `MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Matematik 2b för grundlärare 4-6` → `MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Matematik 2a för grundlärare F-3` → `MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`Matematik 2b för grundlärare F-3` → `MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`Matematik 2a för grundlärare 4-6` → `MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>ARK29H</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`Matematik 2b för grundlärare 4-6` → `MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>ARK29J</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ARK29H</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1410,19 +1410,19 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ARK29J</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Extern redovisning` → `FEA037` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Extern redovisning` → `FEA037` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,152 +1486,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Perspektiv på företagande` → `FEA058` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>RK3043</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>RKA</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>GRV266</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>`Extern redovisning` → `FEA037` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>RV1003</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>`Extern redovisning` → `FEA037` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>RV1055</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Refererar troligen nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Perspektiv på företagande'</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>RV1055</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>`Perspektiv på företagande` → `FEA058` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E44"/>
+  <autoFilter ref="A1:E39"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1709,16 +1574,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -553,12 +553,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GBQ2NP</t>
+          <t>AHI23V</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -573,19 +573,19 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GBQ2QB</t>
+          <t>AHI23W</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -600,19 +600,19 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2QB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U9</t>
+          <t>HI2014</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -627,46 +627,46 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GBQ2UD</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Demography and Markets for Tourism'</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AHI23V</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Tourism and Destination Development – An Introduction` → `TR1009` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AHI23W</t>
+          <t>KG1022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Nordisk turism` → `KG1026` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HI2014</t>
+          <t>KG1027</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -730,51 +730,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Introduktion till Javaprogrammering` → `IK1046` (nedlagd 2020-06-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>GLP29S</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Demography and Markets for Tourism'</t>
+          <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>GLP2KH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Tourism and Destination Development – An Introduction` → `TR1009` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
+          <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>KG1022</t>
+          <t>LP1054</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Nordisk turism` → `KG1026` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
+          <t>`Audiovisuell representation I` → `LP1017` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>KG1027</t>
+          <t>LP1054</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Introduktion till Javaprogrammering` → `IK1046` (nedlagd 2020-06-11); förkunskap nämner nedlagd kurs</t>
+          <t>`Audiovisuell representation II` → `LP1020` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GLP29S</t>
+          <t>GMN3EJ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
+          <t>`Audioteknologi` → `LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GLP2KH</t>
+          <t>GMN3F2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>LP1054</t>
+          <t>GPA2P7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Audiovisuell representation I` → `LP1017` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>LP1054</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Audiovisuell representation II` → `LP1020` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Organisation - roller och intressenter` → `GPA356` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GMN3EJ</t>
+          <t>GPA354</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`Audioteknologi` → `LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
+          <t>`Arbetsrättens grunder` → `PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GMN3F2</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GPA354</t>
+          <t>PA2010</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`Arbetsrättens grunder` → `PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>APG246</t>
+          <t>PA2011</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Matematik 2a för grundlärare F-3` → `MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`Matematik 2a för grundlärare F-3` → `MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Matematik 2b för grundlärare F-3` → `MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`Matematik 2b för grundlärare F-3` → `MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Matematik 2a för grundlärare 4-6` → `MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`Matematik 2a för grundlärare 4-6` → `MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+          <t>`Matematik 2b för grundlärare 4-6` → `MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`Matematik 2b för grundlärare 4-6` → `MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>ARK29H</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ARK29H</t>
+          <t>ARK29J</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1302,14 +1302,14 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ARK29J</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1329,14 +1329,14 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1383,19 +1383,19 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Extern redovisning` → `FEA037` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1437,14 +1437,14 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,44 +1459,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Extern redovisning` → `FEA037` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Perspektiv på företagande` → `FEA058` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>RV1055</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>`Perspektiv på företagande` → `FEA058` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E39"/>
+  <autoFilter ref="A1:E38"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1572,8 +1545,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`Extern redovisning` → `FEA037` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Extern redovisning` → `FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Extern redovisning` → `FEA037` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Extern redovisning` → `FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Perspektiv på företagande` → `FEA058` (nedlagd 2008-03-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Perspektiv på företagande` → `FÖ1057` (nedlagd 2021-02-15); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$G$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP253</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP254</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2014-09-19</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Audiovisuella studier: Kunskapsproduktion och gestaltning'</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AU3005</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
         </is>
@@ -590,15 +626,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
         </is>
@@ -617,15 +659,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
         </is>
@@ -644,15 +692,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>2009-02-24</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Demography and Markets for Tourism'</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
@@ -671,15 +725,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2009-02-24</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>`Tourism and Destination Development – An Introduction` → `TR1009` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
@@ -698,15 +758,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>2010-02-23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2012-11-28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>`Nordisk turism` → `KG1026` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
         </is>
@@ -725,15 +795,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2010-09-07</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>`Introduktion till Javaprogrammering` → `IK1046` (nedlagd 2020-06-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
         </is>
@@ -752,15 +828,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
         </is>
@@ -779,15 +861,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
         </is>
@@ -806,15 +894,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>`Audiovisuell representation I` → `LP1017` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
         </is>
@@ -833,15 +927,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>`Audiovisuell representation II` → `LP1020` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
         </is>
@@ -860,15 +960,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>`Audioteknologi` → `LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
         </is>
@@ -887,15 +993,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
@@ -914,15 +1026,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2021-03-11</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
@@ -941,15 +1059,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>`Organisation - roller och intressenter` → `GPA356` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
@@ -968,15 +1092,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>`Arbetsrättens grunder` → `PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
         </is>
@@ -995,15 +1125,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
@@ -1022,15 +1158,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
@@ -1049,15 +1191,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
@@ -1076,15 +1224,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>`Matematik 2a för grundlärare F-3` → `MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
@@ -1103,15 +1257,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>`Matematik 2b för grundlärare F-3` → `MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
@@ -1130,15 +1290,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>`Matematik 2a för grundlärare 4-6` → `MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
@@ -1157,15 +1323,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>`Matematik 2b för grundlärare 4-6` → `MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
@@ -1184,15 +1356,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
@@ -1211,15 +1389,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
@@ -1238,15 +1422,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
@@ -1265,15 +1455,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
         </is>
@@ -1292,15 +1488,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
         </is>
@@ -1319,15 +1521,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
@@ -1346,15 +1554,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
@@ -1373,15 +1587,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2014-09-19</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
@@ -1400,15 +1620,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>`Extern redovisning` → `FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
@@ -1427,15 +1653,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2007-01-10</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>`Extern redovisning` → `FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
@@ -1454,97 +1686,103 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>`Perspektiv på företagande` → `FÖ1057` (nedlagd 2021-02-15); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E38"/>
+  <autoFilter ref="A1:G38"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Förslag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Länk</t>
         </is>
       </c>
@@ -508,7 +514,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP253</t>
         </is>
@@ -541,7 +552,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP254</t>
         </is>
@@ -574,7 +590,8 @@
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Audiovisuella studier: Kunskapsproduktion och gestaltning'</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AU3005</t>
         </is>
@@ -607,7 +624,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
         </is>
@@ -640,7 +662,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
         </is>
@@ -673,7 +700,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
         </is>
@@ -706,7 +738,8 @@
           <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Demography and Markets for Tourism'</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
@@ -739,7 +772,12 @@
           <t>`Tourism and Destination Development – An Introduction` → `TR1009` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>`TR1009` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
@@ -776,7 +814,12 @@
           <t>`Nordisk turism` → `KG1026` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>`KG1026` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
         </is>
@@ -809,7 +852,12 @@
           <t>`Introduktion till Javaprogrammering` → `IK1046` (nedlagd 2020-06-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>`IK1046` (nedlagd 2020-06-11); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
         </is>
@@ -842,7 +890,12 @@
           <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>`LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
         </is>
@@ -875,7 +928,12 @@
           <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>`LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
         </is>
@@ -908,7 +966,12 @@
           <t>`Audiovisuell representation I` → `LP1017` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>`LP1017` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
         </is>
@@ -941,7 +1004,12 @@
           <t>`Audiovisuell representation II` → `LP1020` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>`LP1020` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
         </is>
@@ -974,7 +1042,12 @@
           <t>`Audioteknologi` → `LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>`LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
         </is>
@@ -1007,7 +1080,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
@@ -1040,7 +1118,12 @@
           <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
@@ -1073,7 +1156,12 @@
           <t>`Organisation - roller och intressenter` → `GPA356` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>`GPA356` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
@@ -1106,7 +1194,12 @@
           <t>`Arbetsrättens grunder` → `PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>`PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
         </is>
@@ -1139,7 +1232,12 @@
           <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
@@ -1172,7 +1270,12 @@
           <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
@@ -1205,7 +1308,12 @@
           <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
@@ -1238,7 +1346,12 @@
           <t>`Matematik 2a för grundlärare F-3` → `MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>`MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
@@ -1271,7 +1384,12 @@
           <t>`Matematik 2b för grundlärare F-3` → `MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>`MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
@@ -1304,7 +1422,12 @@
           <t>`Matematik 2a för grundlärare 4-6` → `MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>`MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
@@ -1337,7 +1460,12 @@
           <t>`Matematik 2b för grundlärare 4-6` → `MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>`MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
@@ -1370,7 +1498,12 @@
           <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>`IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
@@ -1403,7 +1536,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
@@ -1436,7 +1574,12 @@
           <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
@@ -1469,7 +1612,12 @@
           <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
         </is>
@@ -1502,7 +1650,12 @@
           <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
         </is>
@@ -1535,7 +1688,12 @@
           <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
@@ -1568,7 +1726,12 @@
           <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
@@ -1601,7 +1764,12 @@
           <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
@@ -1634,7 +1802,12 @@
           <t>`Extern redovisning` → `FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
@@ -1667,7 +1840,12 @@
           <t>`Extern redovisning` → `FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
@@ -1700,89 +1878,94 @@
           <t>`Perspektiv på företagande` → `FÖ1057` (nedlagd 2021-02-15); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>`FÖ1057` (nedlagd 2021-02-15); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G38"/>
+  <autoFilter ref="A1:H38"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Tourism and Destination Development – An Introduction` → `TR1009` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
+          <t>`Tourism and Destination Development – An Introduction`</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Nordisk turism` → `KG1026` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
+          <t>`Nordisk turism`</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Introduktion till Javaprogrammering` → `IK1046` (nedlagd 2020-06-11); förkunskap nämner nedlagd kurs</t>
+          <t>`Introduktion till Javaprogrammering`</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
+          <t>`Radioproduktion`</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Radioproduktion` → `LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
+          <t>`Radioproduktion`</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Audiovisuell representation I` → `LP1017` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Audiovisuell representation I`</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`Audiovisuell representation II` → `LP1020` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Audiovisuell representation II`</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`Audioteknologi` → `LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
+          <t>`Audioteknologi`</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`Organisation - roller och intressenter` → `GPA356` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`Organisation - roller och intressenter`</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>`Arbetsrättens grunder` → `PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`Arbetsrättens grunder`</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I` → `GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`Matematik 2a för grundlärare F-3` → `MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Matematik 2a för grundlärare F-3`</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`Matematik 2b för grundlärare F-3` → `MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+          <t>`Matematik 2b för grundlärare F-3`</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>`Matematik 2a för grundlärare 4-6` → `MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+          <t>`Matematik 2a för grundlärare 4-6`</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`Matematik 2b för grundlärare 4-6` → `MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+          <t>`Matematik 2b för grundlärare 4-6`</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`Idrott` → `IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Idrott`</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori` → `GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Religionsvetenskap III`</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Religionsvetenskap III`</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Religionsvetenskap III`</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Religionsvetenskap III`</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III` → `GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`Religionsvetenskap III`</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>`Extern redovisning` → `FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Extern redovisning`</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>`Extern redovisning` → `FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
+          <t>`Extern redovisning`</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>`Perspektiv på företagande` → `FÖ1057` (nedlagd 2021-02-15); förkunskap nämner nedlagd kurs</t>
+          <t>`Perspektiv på företagande`</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -866,17 +866,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GLP29S</t>
+          <t>GMN3EJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -887,34 +887,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Radioproduktion`</t>
+          <t>`Audioteknologi`</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>`LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GLP2KH</t>
+          <t>GMN3F2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -925,34 +925,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Radioproduktion`</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>`LP1061` (nedlagd 2021-10-28); förkunskap nämner nedlagd kurs</t>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LP1054</t>
+          <t>GPA2P7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -963,34 +963,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Audiovisuell representation I`</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>`LP1017` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LP1054</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1001,34 +1001,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`Audiovisuell representation II`</t>
+          <t>`Organisation - roller och intressenter`</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>`LP1020` (nedlagd 2020-05-12); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA356` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GMN3EJ</t>
+          <t>GPA354</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1039,34 +1039,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`Audioteknologi`</t>
+          <t>`Arbetsrättens grunder`</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>`LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
+          <t>`PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GMN3F2</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1077,24 +1077,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GPA2P7</t>
+          <t>PA2010</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1125,14 +1125,14 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>PA2011</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1153,34 +1153,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`Organisation - roller och intressenter`</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>`GPA356` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GPA354</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1191,34 +1191,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>`Arbetsrättens grunder`</t>
+          <t>`Matematik 2a för grundlärare F-3`</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>`PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1229,34 +1229,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
+          <t>`Matematik 2b för grundlärare F-3`</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PA2010</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1267,34 +1267,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
+          <t>`Matematik 2a för grundlärare 4-6`</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>PA2011</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1305,24 +1305,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
+          <t>`Matematik 2b för grundlärare 4-6`</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2013-07-03</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1343,34 +1343,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`Matematik 2a för grundlärare F-3`</t>
+          <t>`Idrott`</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>`MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+          <t>`IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1381,34 +1381,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`Matematik 2b för grundlärare F-3`</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>`MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1419,34 +1419,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>`Matematik 2a för grundlärare 4-6`</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>`MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>ARK29H</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1457,34 +1457,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`Matematik 2b för grundlärare 4-6`</t>
+          <t>`Religionsvetenskap III`</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>`MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>ARK29J</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2013-07-03</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1495,24 +1495,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`Idrott`</t>
+          <t>`Religionsvetenskap III`</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>`IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1533,24 +1533,24 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Religionsvetenskap III`</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1571,24 +1571,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Religionsvetenskap III`</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ARK29H</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1619,24 +1619,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ARK29J</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1647,34 +1647,34 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Extern redovisning`</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1685,34 +1685,34 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Extern redovisning`</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1723,174 +1723,22 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Perspektiv på företagande`</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`FÖ1057` (nedlagd 2021-02-15); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>RK3043</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>RKA</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>`Religionsvetenskap III`</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>GRV266</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2019-02-21</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>`Extern redovisning`</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>RV1003</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2007-01-10</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>`Extern redovisning`</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>RV1055</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2016-03-03</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>`Perspektiv på företagande`</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>`FÖ1057` (nedlagd 2021-02-15); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H38"/>
+  <autoFilter ref="A1:H34"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -1958,14 +1806,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -866,17 +866,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GMN3EJ</t>
+          <t>GLP29U</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2019-06-17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -887,34 +887,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Audioteknologi`</t>
+          <t>`Audioteknologi 2`</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>`LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1080` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29U</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GMN3F2</t>
+          <t>GLP2BQ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -925,34 +925,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GPA2P7</t>
+          <t>GLP2CX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -963,34 +963,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
+          <t>`Audioteknologi 1`</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`GLP2JZ` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>GLP2NL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1001,34 +1001,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`Organisation - roller och intressenter`</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>`GPA356` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GPA354</t>
+          <t>GLP2NN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1039,34 +1039,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`Arbetsrättens grunder`</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>`PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>GLP2VT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1077,34 +1077,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
+          <t>`Inspelning i studio`</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`GLP29X` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>PA2010</t>
+          <t>GLP2VT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1115,34 +1115,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
+          <t>`Liveljud och liveinspelning`</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1064` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>PA2011</t>
+          <t>GLP2VT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1153,34 +1153,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
+          <t>`Audioteknologi 2`</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1080` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>GLP2WP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1191,34 +1191,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>`Matematik 2a för grundlärare F-3`</t>
+          <t>`Inspelning i studio`</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>`MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+          <t>`GLP29X` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>GLP2WP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1229,34 +1229,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`Matematik 2b för grundlärare F-3`</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>`MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>GLP32S</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1267,34 +1267,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`Matematik 2a för grundlärare 4-6`</t>
+          <t>`Inspelning i studio`</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>`MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+          <t>`GLP29X` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>GLP32S</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1305,34 +1305,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`Matematik 2b för grundlärare 4-6`</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>`MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>LP1074</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2013-07-03</t>
+          <t>2016-02-19</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1343,34 +1343,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`Idrott`</t>
+          <t>`Inspelning i studio`</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>`IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+          <t>`GLP29X` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1074</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GMN3EJ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1381,34 +1381,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Audioteknologi`</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>GMN3F2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1429,24 +1429,24 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ARK29H</t>
+          <t>GPA2P7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1457,34 +1457,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ARK29J</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1495,34 +1495,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Organisation - roller och intressenter`</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA356` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>GPA354</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1533,34 +1533,34 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Arbetsrättens grunder`</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1571,34 +1571,34 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>PA2010</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1609,34 +1609,34 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>PA2011</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1647,34 +1647,34 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`Extern redovisning`</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2007-01-10</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1685,34 +1685,34 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>`Extern redovisning`</t>
+          <t>`Matematik 2a för grundlärare F-3`</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
+          <t>`MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1723,22 +1723,516 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>`Matematik 2b för grundlärare F-3`</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>`MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>APG276</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>`Matematik 2a för grundlärare 4-6`</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>`MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>APG276</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>`Matematik 2b för grundlärare 4-6`</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>`MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>PG3025</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>`Idrott`</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>`IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ARK25B</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori`</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ARK25C</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori`</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ARK29H</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III`</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ARK29J</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III`</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>GRK2R7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III`</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>GRK2R8</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III`</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RK3043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2014-09-19</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III`</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GRV266</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>`Extern redovisning`</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RV1003</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2007-01-10</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>`Extern redovisning`</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>RV1055</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>`Perspektiv på företagande`</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>`FÖ1057` (nedlagd 2021-02-15); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H34"/>
+  <autoFilter ref="A1:H47"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -1806,6 +2300,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Förkunskapskrav.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Förkunskapskrav" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Förkunskapskrav'!$A$1:$H$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -600,17 +600,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AHI23V</t>
+          <t>AU3005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2020-01-30</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -621,24 +621,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Kunskapsproduktion och gestaltning`</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`AU3002` (nedlagd 2025-12-03); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AU3005</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AHI23W</t>
+          <t>AHI23V</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -669,14 +669,14 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HI2014</t>
+          <t>AHI23W</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
+          <t>2020-01-30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -707,58 +707,62 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>AHI263</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2009-02-24</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Refererar troligen nedlagd kurs</t>
+          <t>Refererar bekräftat nedlagd kurs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Demography and Markets for Tourism'</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>`Religion och politik i afrikanska samhällen`</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>`HI3002` (nedlagd 2017-10-31); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>AHI263</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2009-02-24</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -769,41 +773,37 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Tourism and Destination Development – An Introduction`</t>
+          <t>`Forskningsprojektets planering`</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>`TR1009` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
+          <t>`HI3015` (nedlagd 2017-10-31); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KG1022</t>
+          <t>AHI26P</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2010-02-23</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2012-11-28</t>
-        </is>
-      </c>
+          <t>2021-02-25</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -811,34 +811,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Nordisk turism`</t>
+          <t>`Religion och politik i afrikanska samhällen`</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>`KG1026` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
+          <t>`HI3002` (nedlagd 2017-10-31); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI26P</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KG1027</t>
+          <t>AS3013</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2010-09-07</t>
+          <t>2017-09-26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -849,34 +849,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Introduktion till Javaprogrammering`</t>
+          <t>`Afrikanska samhällen i förändring`</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>`IK1046` (nedlagd 2020-06-11); förkunskap nämner nedlagd kurs</t>
+          <t>`HI3001` (nedlagd 2017-10-31); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3013</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GLP29U</t>
+          <t>AS3013</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2017-09-26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -887,34 +887,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Audioteknologi 2`</t>
+          <t>`Religion och politik i afrikanska samhällen`</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>`LP1080` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
+          <t>`HI3002` (nedlagd 2017-10-31); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3013</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GLP2BQ</t>
+          <t>AS3013</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2017-09-26</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -925,34 +925,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
+          <t>`Forskningsprojektets planering`</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
+          <t>`HI3015` (nedlagd 2017-10-31); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3013</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GLP2CX</t>
+          <t>AS3013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2020-01-31</t>
+          <t>2017-09-26</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -963,34 +963,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Audioteknologi 1`</t>
+          <t>`Den vidareutvecklade forskningsplanen`</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>`GLP2JZ` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
+          <t>`HI3005` (nedlagd 2017-10-31); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3013</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GLP2NL</t>
+          <t>AS3020</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2017-09-26</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1001,34 +1001,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
+          <t>`Afrikanska samhällen i förändring`</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
+          <t>`HI3001` (nedlagd 2017-10-31); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GLP2NN</t>
+          <t>AS3020</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2017-09-26</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1039,34 +1039,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
+          <t>`Religion och politik i afrikanska samhällen`</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
+          <t>`HI3002` (nedlagd 2017-10-31); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GLP2VT</t>
+          <t>AS3020</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
+          <t>2017-09-26</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1077,34 +1077,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>`Inspelning i studio`</t>
+          <t>`Forskningsprojektets planering`</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>`GLP29X` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
+          <t>`HI3015` (nedlagd 2017-10-31); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GLP2VT</t>
+          <t>HI2014</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
+          <t>2016-02-05</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1115,72 +1115,68 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>`Liveljud och liveinspelning`</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>`LP1064` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GLP2VT</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
+          <t>2009-02-24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Refererar bekräftat nedlagd kurs</t>
+          <t>Refererar troligen nedlagd kurs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`Audioteknologi 2`</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>`LP1080` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
-        </is>
-      </c>
+          <t>Refererad kurs hittas ej i vaulten (troligen nedlagd): 'Demography and Markets for Tourism'</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GLP2WP</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2009-02-24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1191,37 +1187,41 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>`Inspelning i studio`</t>
+          <t>`Tourism and Destination Development – An Introduction`</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>`GLP29X` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
+          <t>`TR1009` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GLP2WP</t>
+          <t>KG1022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>2010-02-23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2012-11-28</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Refererar bekräftat nedlagd kurs</t>
@@ -1229,34 +1229,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
+          <t>`Nordisk turism`</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
+          <t>`KG1026` (nedlagd 2019-04-02); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GLP32S</t>
+          <t>KG1027</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2010-09-07</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1267,24 +1267,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`Inspelning i studio`</t>
+          <t>`Introduktion till Javaprogrammering`</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>`GLP29X` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
+          <t>`IK1046` (nedlagd 2020-06-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GLP32S</t>
+          <t>GLP29U</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2019-06-17</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1305,24 +1305,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
+          <t>`Audioteknologi 2`</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1080` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29U</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>LP1074</t>
+          <t>GLP2BQ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2016-02-19</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1343,34 +1343,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`Inspelning i studio`</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>`GLP29X` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GMN3EJ</t>
+          <t>GLP2CX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1381,34 +1381,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`Audioteknologi`</t>
+          <t>`Audioteknologi 1`</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>`LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
+          <t>`GLP2JZ` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GMN3F2</t>
+          <t>GLP2NL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1419,34 +1419,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GPA2P7</t>
+          <t>GLP2NN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1457,34 +1457,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>GLP2VT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1495,34 +1495,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`Organisation - roller och intressenter`</t>
+          <t>`Inspelning i studio`</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>`GPA356` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`GLP29X` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GPA354</t>
+          <t>GLP2VT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1533,34 +1533,34 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`Arbetsrättens grunder`</t>
+          <t>`Liveljud och liveinspelning`</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>`PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1064` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>GLP2VT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1571,34 +1571,34 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
+          <t>`Audioteknologi 2`</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1080` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PA2010</t>
+          <t>GLP2WP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1609,34 +1609,34 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
+          <t>`Inspelning i studio`</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`GLP29X` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>PA2011</t>
+          <t>GLP2WP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1647,34 +1647,34 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>GLP32S</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1685,34 +1685,34 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>`Matematik 2a för grundlärare F-3`</t>
+          <t>`Inspelning i studio`</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>`MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+          <t>`GLP29X` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>GLP32S</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1723,34 +1723,34 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>`Matematik 2b för grundlärare F-3`</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>`MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1065` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>LP1074</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2016-02-19</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1761,34 +1761,34 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>`Matematik 2a för grundlärare 4-6`</t>
+          <t>`Inspelning i studio`</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>`MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+          <t>`GLP29X` (nedlagd 2026-06-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1074</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>GMN3EJ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1799,34 +1799,34 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>`Matematik 2b för grundlärare 4-6`</t>
+          <t>`Audioteknologi`</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>`MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+          <t>`LP1027` (nedlagd 2021-02-22); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EJ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>GMN3F2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2013-07-03</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1837,34 +1837,34 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>`Idrott`</t>
+          <t>`Vetenskapsteori`</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>`IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GPA2P7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1875,34 +1875,34 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1913,34 +1913,34 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori`</t>
+          <t>`Organisation - roller och intressenter`</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA356` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ARK29H</t>
+          <t>GPA354</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1951,34 +1951,34 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Arbetsrättens grunder`</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`PA1021` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ARK29J</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1989,34 +1989,34 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>PA2010</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2027,34 +2027,34 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>PA2011</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2065,34 +2065,34 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Samhällsvetenskaplig metod och vetenskapsteori I`</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`GPA32R` (nedlagd 2026-02-11); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2103,34 +2103,34 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>`Religionsvetenskap III`</t>
+          <t>`Matematik 2a för grundlärare F-3`</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+          <t>`MD2017` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2141,34 +2141,34 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>`Extern redovisning`</t>
+          <t>`Matematik 2b för grundlärare F-3`</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
+          <t>`MD2019` (nedlagd 2021-04-12); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2007-01-10</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2179,34 +2179,34 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>`Extern redovisning`</t>
+          <t>`Matematik 2a för grundlärare 4-6`</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
+          <t>`MD2016` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -2217,22 +2217,440 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>`Matematik 2b för grundlärare 4-6`</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>`MD2018` (nedlagd 2022-08-29); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>PG3025</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>`Idrott`</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>`IDB009` (nedlagd 2005-08-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ARK25B</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori`</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>ARK25C</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori`</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>`GPG263` (nedlagd 2024-03-25); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>ARK29H</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III`</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>ARK29J</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III`</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29J</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>GRK2R7</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III`</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GRK2R8</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III`</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>RK3043</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2014-09-19</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>`Religionsvetenskap III`</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>`GRK25S` (nedlagd 2023-03-01); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>GRV266</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>`Extern redovisning`</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>RV1003</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2007-01-10</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>`Extern redovisning`</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>`FÖ1004` (nedlagd 2016-01-18); förkunskap nämner nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>RV1055</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Refererar bekräftat nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>`Perspektiv på företagande`</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>`FÖ1057` (nedlagd 2021-02-15); förkunskap nämner nedlagd kurs</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H47"/>
+  <autoFilter ref="A1:H58"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -2326,6 +2744,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId114"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
